--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -193,7 +193,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">English</t>
+          <t xml:space="preserve">Vietnamese</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -247,7 +247,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">good morning</t>
+          <t xml:space="preserve">chào buổi sáng</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -274,7 +274,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">thank you for your help</t>
+          <t xml:space="preserve">cảm ơn bạn đã giúp đỡ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -301,7 +301,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">please say that again</t>
+          <t xml:space="preserve">làm ơn nói lại một lần nữa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -328,7 +328,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">I don't understand (by ear)</t>
+          <t xml:space="preserve">tôi nghe không hiểu</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -355,7 +355,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">how much does it cost</t>
+          <t xml:space="preserve">bao nhiêu tiền</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -382,7 +382,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">where is the toilet</t>
+          <t xml:space="preserve">nhà vệ sinh ở đâu</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">I; me</t>
+          <t xml:space="preserve">tôi</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">you</t>
+          <t xml:space="preserve">bạn</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">good; well</t>
+          <t xml:space="preserve">tốt; khỏe</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">to be</t>
+          <t xml:space="preserve">là</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">person</t>
+          <t xml:space="preserve">người</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">big</t>
+          <t xml:space="preserve">to; lớn</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">small</t>
+          <t xml:space="preserve">nhỏ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">water</t>
+          <t xml:space="preserve">nước</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">to study</t>
+          <t xml:space="preserve">học</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">to love</t>
+          <t xml:space="preserve">yêu</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">day; sky</t>
+          <t xml:space="preserve">trời; ngày</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">moon; month</t>
+          <t xml:space="preserve">trăng; tháng</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">home; family</t>
+          <t xml:space="preserve">nhà; gia đình</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">middle; China</t>
+          <t xml:space="preserve">giữa; Trung Quốc</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">country</t>
+          <t xml:space="preserve">nước; quốc gia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">vehicle</t>
+          <t xml:space="preserve">xe</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">mountain</t>
+          <t xml:space="preserve">núi</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">sun; day</t>
+          <t xml:space="preserve">mặt trời; ngày</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">fire</t>
+          <t xml:space="preserve">lửa</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">mouth; opening</t>
+          <t xml:space="preserve">miệng; cửa</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">hand</t>
+          <t xml:space="preserve">tay</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">heart</t>
+          <t xml:space="preserve">tim; lòng</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">horse</t>
+          <t xml:space="preserve">ngựa</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">wood; tree</t>
+          <t xml:space="preserve">gỗ; cây</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">field</t>
+          <t xml:space="preserve">ruộng</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Japanese language</t>
+          <t xml:space="preserve">tiếng Nhật</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">library</t>
+          <t xml:space="preserve">thư viện</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I am a student.</t>
+          <t xml:space="preserve">Tôi là học sinh.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">a new book</t>
+          <t xml:space="preserve">một quyển sách mới</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">I walk to the station.</t>
+          <t xml:space="preserve">Tôi đi bộ đến ga.</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the teacher's talk</t>
+          <t xml:space="preserve">câu chuyện của thầy giáo</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dictionary</t>
+          <t xml:space="preserve">từ điển</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">to practise; exercise</t>
+          <t xml:space="preserve">luyện tập; bài tập</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">to translate; translator</t>
+          <t xml:space="preserve">dịch; phiên dịch viên</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stroke (of a character)</t>
+          <t xml:space="preserve">nét (của chữ Hán)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">radical</t>
+          <t xml:space="preserve">bộ thủ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tone</t>
+          <t xml:space="preserve">thanh điệu</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beijing, the capital</t>
+          <t xml:space="preserve">Bắc Kinh, thủ đô</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shanghai, the largest city</t>
+          <t xml:space="preserve">Thượng Hải, thành phố lớn nhất</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guangzhou</t>
+          <t xml:space="preserve">Quảng Châu</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hangzhou</t>
+          <t xml:space="preserve">Hàng Châu</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anhui province</t>
+          <t xml:space="preserve">tỉnh An Huy</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chang'an, the Tang capital</t>
+          <t xml:space="preserve">Trường An, kinh đô thời Đường</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tianjin — switched off, so it never reaches Anki</t>
+          <t xml:space="preserve">Thiên Tân — dòng này đang tắt nên không bao giờ vào Anki</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">library</t>
+          <t xml:space="preserve">thư viện</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">aeroplane</t>
+          <t xml:space="preserve">máy bay</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hospital</t>
+          <t xml:space="preserve">bệnh viện</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">season</t>
+          <t xml:space="preserve">mùa</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">habit; to be used to</t>
+          <t xml:space="preserve">thói quen; quen với</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">environment</t>
+          <t xml:space="preserve">môi trường</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">English</t>
+          <t xml:space="preserve">Vietnamese</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">to read</t>
+          <t xml:space="preserve">đọc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">to write</t>
+          <t xml:space="preserve">viết</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">to listen</t>
+          <t xml:space="preserve">nghe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">to speak</t>
+          <t xml:space="preserve">nói</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">to remember</t>
+          <t xml:space="preserve">nhớ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">to forget</t>
+          <t xml:space="preserve">quên</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">English</t>
+          <t xml:space="preserve">Vietnamese</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">the tree</t>
+          <t xml:space="preserve">cái cây</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">the city</t>
+          <t xml:space="preserve">thành phố</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">the heart</t>
+          <t xml:space="preserve">trái tim</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">quickly</t>
+          <t xml:space="preserve">nhanh chóng</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">the bird</t>
+          <t xml:space="preserve">con chim</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the moon</t>
+          <t xml:space="preserve">mặt trăng</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">the mountain</t>
+          <t xml:space="preserve">ngọn núi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">the river</t>
+          <t xml:space="preserve">con sông</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">I am Chinese.</t>
+          <t xml:space="preserve">Tôi là người Trung Quốc.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">He is reading in the library.</t>
+          <t xml:space="preserve">Anh ấy đang đọc sách trong thư viện.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">We are going to Beijing tomorrow.</t>
+          <t xml:space="preserve">Ngày mai chúng tôi đi Bắc Kinh.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">This book is very interesting.</t>
+          <t xml:space="preserve">Quyển sách này rất thú vị.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">She can speak three languages.</t>
+          <t xml:space="preserve">Cô ấy nói được ba thứ tiếng.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Please close the door.</t>
+          <t xml:space="preserve">Làm ơn đóng cửa lại.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cat</t>
+          <t xml:space="preserve">con mèo</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">panda</t>
+          <t xml:space="preserve">gấu trúc</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">tea</t>
+          <t xml:space="preserve">trà</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Great Wall</t>
+          <t xml:space="preserve">Vạn Lý Trường Thành</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Terracotta Army</t>
+          <t xml:space="preserve">đội quân đất nung</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">apple</t>
+          <t xml:space="preserve">quả táo</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">tiger</t>
+          <t xml:space="preserve">con hổ</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">horse</t>
+          <t xml:space="preserve">con ngựa</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">the moon</t>
+          <t xml:space="preserve">mặt trăng</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">fire</t>
+          <t xml:space="preserve">lửa</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">mountain</t>
+          <t xml:space="preserve">núi</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beijing — the capital</t>
+          <t xml:space="preserve">Bắc Kinh — thủ đô</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shanghai</t>
+          <t xml:space="preserve">Thượng Hải</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guangzhou</t>
+          <t xml:space="preserve">Quảng Châu</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hangzhou</t>
+          <t xml:space="preserve">Hàng Châu</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tianjin</t>
+          <t xml:space="preserve">Thiên Tân</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anhui province</t>
+          <t xml:space="preserve">tỉnh An Huy</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taiwan</t>
+          <t xml:space="preserve">Đài Loan</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chang'an — the Tang capital</t>
+          <t xml:space="preserve">Trường An — kinh đô thời Đường</t>
         </is>
       </c>
     </row>

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -13,10 +13,11 @@
     <sheet name="09 Video" sheetId="9" r:id="rId9"/>
     <sheet name="10 Speech" sheetId="10" r:id="rId10"/>
     <sheet name="11 Chinese writing" sheetId="11" r:id="rId11"/>
-    <sheet name="12 Japanese furigana" sheetId="12" r:id="rId12"/>
-    <sheet name="13 Any language headers" sheetId="13" r:id="rId13"/>
-    <sheet name="14 Everything" sheetId="14" r:id="rId14"/>
-    <sheet name="15 Edge cases" sheetId="15" r:id="rId15"/>
+    <sheet name="12 Chinese drawing" sheetId="12" r:id="rId12"/>
+    <sheet name="13 Japanese furigana" sheetId="13" r:id="rId13"/>
+    <sheet name="14 Any language headers" sheetId="14" r:id="rId14"/>
+    <sheet name="15 Everything" sheetId="15" r:id="rId15"/>
+    <sheet name="16 Edge cases" sheetId="16" r:id="rId16"/>
   </sheets>
 </workbook>
 </file>
@@ -1537,17 +1538,37 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japanese</t>
+          <t xml:space="preserve">SUBDECK 1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">TAGS</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Meaning</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note</t>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pinyin</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Draw</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Character</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Example</t>
         </is>
       </c>
     </row>
@@ -1557,131 +1578,533 @@
           <t xml:space="preserve">#config</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">size=40; furigana</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">size=20</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">size=14; color=muted; hint</t>
+          <t xml:space="preserve">size=24; color=muted; label=Draw the character for</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; size=40; color=accent</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; draw; size=260</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=72; tts=zh_CN</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=18; tts=zh_CN; speed=0.8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">f01</t>
+          <t xml:space="preserve">d01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">日本語[にほんご]</t>
+          <t xml:space="preserve">HSK 1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tiếng Nhật</t>
+          <t xml:space="preserve">hanzi, hsk1, draw</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Write the reading in brackets after the kanji.</t>
+          <t xml:space="preserve">tôi</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wǒ</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我是学生。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">f02</t>
+          <t xml:space="preserve">d02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">図書館[としょかん]</t>
+          <t xml:space="preserve">HSK 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">thư viện</t>
+          <t xml:space="preserve">hanzi, hsk1, draw</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bạn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nǐ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你好吗？</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">f03</t>
+          <t xml:space="preserve">d03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 私[わたし]は 学生[がくせい]です。</t>
+          <t xml:space="preserve">HSK 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tôi là học sinh.</t>
+          <t xml:space="preserve">hanzi, hsk1, draw</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A leading space separates one reading from the previous word.</t>
+          <t xml:space="preserve">tốt; khỏe</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hǎo</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">好</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">好</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">今天天气很好。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">f04</t>
+          <t xml:space="preserve">d04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">新[あたら]しい 本[ほん]</t>
+          <t xml:space="preserve">HSK 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">một quyển sách mới</t>
+          <t xml:space="preserve">hanzi, hsk1, draw</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">người</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rén</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">那个人很高。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">f05</t>
+          <t xml:space="preserve">d05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">駅[えき]まで 歩[ある]きます。</t>
+          <t xml:space="preserve">HSK 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tôi đi bộ đến ga.</t>
+          <t xml:space="preserve">hanzi, hsk1, draw</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to; lớn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dà</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">这个房子很大。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">f06</t>
+          <t xml:space="preserve">d06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">先生[せんせい]の 話[はなし]</t>
+          <t xml:space="preserve">HSK 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">câu chuyện của thầy giáo</t>
+          <t xml:space="preserve">hanzi, hsk1, draw</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nhỏ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xiǎo</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小狗在门口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSK 1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hanzi, hsk1, draw</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nước</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shuǐ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">水</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">水</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我想喝水。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSK 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hanzi, hsk1, draw</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">học</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xué</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">学</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">学</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我在学中文。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSK 1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hanzi, hsk1, draw</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trời; ngày</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tiān</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明天见。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSK 2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hanzi, hsk2, draw</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">núi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shān</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">山</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">山</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">山上有雪。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSK 2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hanzi, hsk2, draw</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lửa</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">huǒ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火车快到了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSK 2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hanzi, hsk2, draw</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">miệng; cửa</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kǒu</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">口</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">口</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">门口有人在等。</t>
         </is>
       </c>
     </row>
@@ -1700,22 +2123,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">汉字</t>
+          <t xml:space="preserve">Japanese</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">拼音</t>
+          <t xml:space="preserve">Meaning</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">释义</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">例句</t>
+          <t xml:space="preserve">Note</t>
         </is>
       </c>
     </row>
@@ -1727,184 +2145,129 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">size=44; tts=zh_CN</t>
+          <t xml:space="preserve">size=40; furigana</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">size=22; color=accent</t>
+          <t xml:space="preserve">size=20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">size=20</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">size=16; color=muted</t>
+          <t xml:space="preserve">size=14; color=muted; hint</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">h01</t>
+          <t xml:space="preserve">f01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">词典</t>
+          <t xml:space="preserve">日本語[にほんご]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cídiǎn</t>
+          <t xml:space="preserve">tiếng Nhật</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">từ điển</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">我买了一本新词典。</t>
+          <t xml:space="preserve">Write the reading in brackets after the kanji.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">h02</t>
+          <t xml:space="preserve">f02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">练习</t>
+          <t xml:space="preserve">図書館[としょかん]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">liànxí</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">luyện tập; bài tập</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">每天练习写汉字。</t>
+          <t xml:space="preserve">thư viện</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">h03</t>
+          <t xml:space="preserve">f03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">翻译</t>
+          <t xml:space="preserve"> 私[わたし]は 学生[がくせい]です。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fānyì</t>
+          <t xml:space="preserve">Tôi là học sinh.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dịch; phiên dịch viên</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">他是一位翻译。</t>
+          <t xml:space="preserve">A leading space separates one reading from the previous word.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">h04</t>
+          <t xml:space="preserve">f04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">笔画</t>
+          <t xml:space="preserve">新[あたら]しい 本[ほん]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bǐhuà</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nét (của chữ Hán)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">“我”有七个笔画。</t>
+          <t xml:space="preserve">một quyển sách mới</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">h05</t>
+          <t xml:space="preserve">f05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">部首</t>
+          <t xml:space="preserve">駅[えき]まで 歩[ある]きます。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">bùshǒu</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bộ thủ</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">这个字的部首是“水”。</t>
+          <t xml:space="preserve">Tôi đi bộ đến ga.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">h06</t>
+          <t xml:space="preserve">f06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">声调</t>
+          <t xml:space="preserve">先生[せんせい]の 話[はなし]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shēngdiào</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thanh điệu</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">普通话有四个声调。</t>
+          <t xml:space="preserve">câu chuyện của thầy giáo</t>
         </is>
       </c>
     </row>
@@ -1923,548 +2286,211 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYNC</t>
+          <t xml:space="preserve">汉字</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUBDECK 1</t>
+          <t xml:space="preserve">拼音</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUBDECK 2</t>
+          <t xml:space="preserve">释义</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUBDECK 3</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TAGS</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Picture</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Word</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pinyin</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meaning</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Example</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recording</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clip</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Source</t>
+          <t xml:space="preserve">例句</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">#config align=left; speed=0.9; reverse</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">image; size=260; label=Look</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=front; size=44; bold; tts=zh_CN; voices=Ting-Ting,Microsoft Huihui</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=back; size=22; color=accent; align=center; type=nc</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=back; size=20</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=back; size=16; color=muted; italic; tts=zh_CN; speed=0.7</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=back; audio; label=Native recording</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=back; video; size=480; hint; label=Watch</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=hide</t>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">size=44; tts=zh_CN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">size=22; color=accent</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">size=20</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">size=16; color=muted</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">e01</t>
+          <t xml:space="preserve">h01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">词典</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Places</t>
+          <t xml:space="preserve">cídiǎn</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">từ điển</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cities</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cities, hsk1</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/f/fa/Great_Wall_of_China_July_2006.JPG/500px-Great_Wall_of_China_July_2006.JPG</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">北京</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Běijīng</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bắc Kinh, thủ đô</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">北京有很多名胜古迹。</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/8/8a/Zh-Beijing.ogg</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.youtube.com/watch?v=jNQXAC9IVRw</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">internal note, never shown</t>
+          <t xml:space="preserve">我买了一本新词典。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">e02</t>
+          <t xml:space="preserve">h02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">练习</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Places</t>
+          <t xml:space="preserve">liànxí</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">luyện tập; bài tập</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cities</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cities</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上海</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shànghǎi</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thượng Hải, thành phố lớn nhất</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上海在长江的入海口。</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/73/Zh-Shanghai.ogg</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">internal note, never shown</t>
+          <t xml:space="preserve">每天练习写汉字。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">e03</t>
+          <t xml:space="preserve">h03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">翻译</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Places</t>
+          <t xml:space="preserve">fānyì</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">dịch; phiên dịch viên</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cities</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cities</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">广州</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Guǎngzhōu</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quảng Châu</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">广州的早茶很有名。</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/8/82/Zh-Guangzhou.ogg</t>
+          <t xml:space="preserve">他是一位翻译。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">e04</t>
+          <t xml:space="preserve">h04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">笔画</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Places</t>
+          <t xml:space="preserve">bǐhuà</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">nét (của chữ Hán)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cities</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cities</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">杭州</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hángzhōu</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hàng Châu</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">杭州有西湖。</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/3/36/Zh-Hangzhou.ogg</t>
+          <t xml:space="preserve">“我”有七个笔画。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">e05</t>
+          <t xml:space="preserve">h05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">部首</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Places</t>
+          <t xml:space="preserve">bùshǒu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">bộ thủ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provinces</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">provinces</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Mount_Everest_as_seen_from_Drukair2_PLW_edit.jpg/500px-Mount_Everest_as_seen_from_Drukair2_PLW_edit.jpg</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">安徽</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ānhuī</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tỉnh An Huy</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">安徽有黄山。</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/5/57/Zh-Anhui.ogg</t>
+          <t xml:space="preserve">这个字的部首是“水”。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">e06</t>
+          <t xml:space="preserve">h06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">声调</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Places</t>
+          <t xml:space="preserve">shēngdiào</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">thanh điệu</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">History</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">history</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Terracotta_Army_Pit_1_-_2.jpg/500px-Terracotta_Army_Pit_1_-_2.jpg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">长安</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cháng'ān</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trường An, kinh đô thời Đường</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">长安是今天的西安。</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/9/9e/Zh-Changan.ogg</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://youtu.be/aircAruvnKk</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">e07</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Places</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">China</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cities</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cities</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">天津</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiānjīn</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thiên Tân — dòng này đang tắt nên không bao giờ vào Anki</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">天津在北京的东边。</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/9/9b/Zh-Tianjin.ogg</t>
+          <t xml:space="preserve">普通话有四个声调。</t>
         </is>
       </c>
     </row>
@@ -2488,6 +2514,566 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">SUBDECK 1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUBDECK 2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUBDECK 3</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAGS</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Picture</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Word</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pinyin</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meaning</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Example</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recording</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clip</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config align=left; speed=0.9; reverse</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">image; size=260; label=Look</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; size=44; bold; tts=zh_CN; voices=Ting-Ting,Microsoft Huihui</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=22; color=accent; align=center; type=nc</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=16; color=muted; italic; tts=zh_CN; speed=0.7</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; audio; label=Native recording</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; video; size=480; hint; label=Watch</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=hide</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Places</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cities</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cities, hsk1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/f/fa/Great_Wall_of_China_July_2006.JPG/500px-Great_Wall_of_China_July_2006.JPG</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">北京</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Běijīng</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bắc Kinh, thủ đô</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">北京有很多名胜古迹。</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/8/8a/Zh-Beijing.ogg</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/watch?v=jNQXAC9IVRw</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">internal note, never shown</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Places</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cities</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cities</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上海</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shànghǎi</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thượng Hải, thành phố lớn nhất</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">上海在长江的入海口。</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/73/Zh-Shanghai.ogg</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">internal note, never shown</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Places</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cities</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cities</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">广州</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guǎngzhōu</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quảng Châu</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">广州的早茶很有名。</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/8/82/Zh-Guangzhou.ogg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Places</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cities</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cities</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杭州</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hángzhōu</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hàng Châu</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杭州有西湖。</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/3/36/Zh-Hangzhou.ogg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Places</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provinces</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">provinces</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Mount_Everest_as_seen_from_Drukair2_PLW_edit.jpg/500px-Mount_Everest_as_seen_from_Drukair2_PLW_edit.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">安徽</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ānhuī</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tỉnh An Huy</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">安徽有黄山。</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/5/57/Zh-Anhui.ogg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Places</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">History</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">history</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Terracotta_Army_Pit_1_-_2.jpg/500px-Terracotta_Army_Pit_1_-_2.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长安</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cháng'ān</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trường An, kinh đô thời Đường</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长安是今天的西安。</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/9/9e/Zh-Changan.ogg</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://youtu.be/aircAruvnKk</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Places</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cities</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cities</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天津</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiānjīn</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thiên Tân — dòng này đang tắt nên không bao giờ vào Anki</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天津在北京的东边。</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/9/9b/Zh-Tianjin.ogg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYNC</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Word</t>
         </is>
       </c>

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -407,12 +407,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUBDECK 1</t>
+          <t xml:space="preserve">TAGS</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAGS</t>
+          <t xml:space="preserve">Level</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -447,9 +447,14 @@
           <t xml:space="preserve">#config</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subdeck=1; side=front; size=14; color=muted; label=HSK level</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">size=24; color=muted; label=Write the character for</t>
+          <t xml:space="preserve">side=front; size=24; color=muted; label=Write the character for</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -481,12 +486,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -523,12 +528,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -565,12 +570,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -607,12 +612,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -649,12 +654,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -691,12 +696,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -733,12 +738,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -775,12 +780,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -817,12 +822,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -859,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -901,12 +906,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -943,12 +948,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -985,12 +990,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1027,12 +1032,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1069,12 +1074,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1111,12 +1116,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1153,12 +1158,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1195,12 +1200,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1237,12 +1242,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1279,12 +1284,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1321,12 +1326,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1363,12 +1368,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1405,12 +1410,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1447,12 +1452,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1489,12 +1494,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t xml:space="preserve">hanzi, hsk3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t xml:space="preserve">HSK 3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hanzi, hsk3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -199,7 +199,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slowly</t>
+          <t xml:space="preserve">Once more, slowly</t>
         </is>
       </c>
     </row>
@@ -226,7 +226,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">side=back; size=14; color=muted; tts=zh_CN; speed=0.5; label=Once more, slowly</t>
+          <t xml:space="preserve">side=hide; tts=zh_CN; speed=0.5</t>
         </is>
       </c>
     </row>

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">subdeck=1; side=front; size=14; color=muted; label=HSK level</t>
+          <t xml:space="preserve">subdeck=1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">size=abc; align</t>
+          <t xml:space="preserve">size=abc; align; subdeck=1; bold</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -2581,7 +2581,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">#config align=left; speed=0.9; reverse</t>
+          <t xml:space="preserve">#config align=left; speed=0.9; reverse; theme=sakura</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3116,7 +3116,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">#config align=middle; spid=3; reverse</t>
+          <t xml:space="preserve">#config align=middle; spid=3; reverse; theme=neon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -3116,7 +3116,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">#config align=middle; spid=3; reverse; theme=neon</t>
+          <t xml:space="preserve">#config align=middle; spid=3; reverse; theme=neon; unsorted=</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3352,49 +3352,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">s01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Geography</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Capitals</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">europe, capitals</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Capital of Portugal?</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lisbon</t>
+          <t xml:space="preserve">#config unsorted=Unsorted</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">s02</t>
+          <t xml:space="preserve">s01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">x</t>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3409,29 +3379,29 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">asia; capitals</t>
+          <t xml:space="preserve">europe, capitals</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capital of Vietnam?</t>
+          <t xml:space="preserve">Capital of Portugal?</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanoi</t>
+          <t xml:space="preserve">Lisbon</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">s03</t>
+          <t xml:space="preserve">s02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">x</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3441,34 +3411,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rivers</t>
+          <t xml:space="preserve">Capitals</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivers</t>
+          <t xml:space="preserve">asia; capitals</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Longest river in Asia?</t>
+          <t xml:space="preserve">Capital of Vietnam?</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Yangtze</t>
+          <t xml:space="preserve">Hanoi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">s04</t>
+          <t xml:space="preserve">s03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRUE</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3483,133 +3453,170 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivers, europe</t>
+          <t xml:space="preserve">rivers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Which river flows through Paris?</t>
+          <t xml:space="preserve">Longest river in Asia?</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Seine</t>
+          <t xml:space="preserve">The Yangtze</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">s05</t>
+          <t xml:space="preserve">s04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">✓</t>
+          <t xml:space="preserve">TRUE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">History</t>
+          <t xml:space="preserve">Geography</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rivers</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">rivers, europe</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who was the first Ming emperor?</t>
+          <t xml:space="preserve">Which river flows through Paris?</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Hongwu Emperor</t>
+          <t xml:space="preserve">The Seine</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">s06</t>
+          <t xml:space="preserve">s05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">✓</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">History</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">A row with no SUBDECK stays in the deck root.</t>
+          <t xml:space="preserve">Who was the first Ming emperor?</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">No subdeck, no tag.</t>
+          <t xml:space="preserve">The Hongwu Emperor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">s07</t>
+          <t xml:space="preserve">s06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Geography</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Capitals</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">capitals</t>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">This row is switched off.</t>
+          <t xml:space="preserve">Where does a row with both SUBDECK cells empty go?</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">It is never written to Anki.</t>
+          <t xml:space="preserve">Into 'Unsorted', because the settings row named it. Without that key it stays in the sheet's own deck, beside the sub-decks.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t xml:space="preserve">s07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Geography</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capitals</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">capitals</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This row is switched off.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It is never written to Anki.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t xml:space="preserve">s08</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">History</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">history</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t xml:space="preserve">An empty SYNC cell is off too.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">Same as 'no'.</t>
         </is>

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -3116,7 +3116,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">#config align=middle; spid=3; reverse; theme=neon; unsorted=</t>
+          <t xml:space="preserve">#config align=middle; spid=3; reverse; theme=neon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3352,19 +3352,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">#config unsorted=Unsorted</t>
+          <t xml:space="preserve">s01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Geography</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capitals</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europe, capitals</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capital of Portugal?</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lisbon</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">s01</t>
+          <t xml:space="preserve">s02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">x</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3379,29 +3409,29 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">europe, capitals</t>
+          <t xml:space="preserve">asia; capitals</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capital of Portugal?</t>
+          <t xml:space="preserve">Capital of Vietnam?</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisbon</t>
+          <t xml:space="preserve">Hanoi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">s02</t>
+          <t xml:space="preserve">s03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">x</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3411,34 +3441,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capitals</t>
+          <t xml:space="preserve">Rivers</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">asia; capitals</t>
+          <t xml:space="preserve">rivers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capital of Vietnam?</t>
+          <t xml:space="preserve">Longest river in Asia?</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanoi</t>
+          <t xml:space="preserve">The Yangtze</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">s03</t>
+          <t xml:space="preserve">s04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">TRUE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3453,170 +3483,133 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivers</t>
+          <t xml:space="preserve">rivers, europe</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Longest river in Asia?</t>
+          <t xml:space="preserve">Which river flows through Paris?</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Yangtze</t>
+          <t xml:space="preserve">The Seine</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">s04</t>
+          <t xml:space="preserve">s05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRUE</t>
+          <t xml:space="preserve">✓</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geography</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rivers</t>
+          <t xml:space="preserve">History</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivers, europe</t>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Which river flows through Paris?</t>
+          <t xml:space="preserve">Who was the first Ming emperor?</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Seine</t>
+          <t xml:space="preserve">The Hongwu Emperor</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">s05</t>
+          <t xml:space="preserve">s06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">✓</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">History</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who was the first Ming emperor?</t>
+          <t xml:space="preserve">Where does a row with both SUBDECK cells empty go?</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Hongwu Emperor</t>
+          <t xml:space="preserve">Into 'Unsorted'. A sheet that sorts its rows has somewhere for the ones it did not sort.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">s06</t>
+          <t xml:space="preserve">s07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Geography</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capitals</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">capitals</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Where does a row with both SUBDECK cells empty go?</t>
+          <t xml:space="preserve">This row is switched off.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Into 'Unsorted', because the settings row named it. Without that key it stays in the sheet's own deck, beside the sub-decks.</t>
+          <t xml:space="preserve">It is never written to Anki.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">s07</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
+          <t xml:space="preserve">s08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geography</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Capitals</t>
+          <t xml:space="preserve">History</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">capitals</t>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">This row is switched off.</t>
+          <t xml:space="preserve">An empty SYNC cell is off too.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">It is never written to Anki.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s08</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">History</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">history</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">An empty SYNC cell is off too.</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">Same as 'no'.</t>
         </is>

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -2,22 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="01 Basic" sheetId="1" r:id="rId1"/>
-    <sheet name="02 Sync and subdecks" sheetId="2" r:id="rId2"/>
-    <sheet name="03 Card layout" sheetId="3" r:id="rId3"/>
-    <sheet name="04 Reverse" sheetId="4" r:id="rId4"/>
-    <sheet name="05 Type the answer" sheetId="5" r:id="rId5"/>
-    <sheet name="06 Cloze" sheetId="6" r:id="rId6"/>
-    <sheet name="07 Images" sheetId="7" r:id="rId7"/>
-    <sheet name="08 Audio" sheetId="8" r:id="rId8"/>
-    <sheet name="09 Video" sheetId="9" r:id="rId9"/>
-    <sheet name="10 Speech" sheetId="10" r:id="rId10"/>
-    <sheet name="11 Chinese writing" sheetId="11" r:id="rId11"/>
-    <sheet name="12 Chinese drawing" sheetId="12" r:id="rId12"/>
-    <sheet name="13 Japanese furigana" sheetId="13" r:id="rId13"/>
-    <sheet name="14 Any language headers" sheetId="14" r:id="rId14"/>
-    <sheet name="15 Everything" sheetId="15" r:id="rId15"/>
-    <sheet name="16 Edge cases" sheetId="16" r:id="rId16"/>
+    <sheet name="01 Basic (cơ bản)" sheetId="1" r:id="rId1"/>
+    <sheet name="02 Sync &amp; subdecks (deck con)" sheetId="2" r:id="rId2"/>
+    <sheet name="03 Card layout (bố cục thẻ)" sheetId="3" r:id="rId3"/>
+    <sheet name="04 Reverse (thẻ ngược)" sheetId="4" r:id="rId4"/>
+    <sheet name="05 Type the answer (gõ đáp án)" sheetId="5" r:id="rId5"/>
+    <sheet name="06 Cloze (điền chỗ trống)" sheetId="6" r:id="rId6"/>
+    <sheet name="07 Images (hình ảnh)" sheetId="7" r:id="rId7"/>
+    <sheet name="08 Audio (âm thanh)" sheetId="8" r:id="rId8"/>
+    <sheet name="09 Video (video nhúng)" sheetId="9" r:id="rId9"/>
+    <sheet name="10 Speech (đọc thành tiếng)" sheetId="10" r:id="rId10"/>
+    <sheet name="11 Chinese writing (gõ chữ)" sheetId="11" r:id="rId11"/>
+    <sheet name="12 Chinese drawing (viết tay)" sheetId="12" r:id="rId12"/>
+    <sheet name="13 Furigana (phiên âm kanji)" sheetId="13" r:id="rId13"/>
+    <sheet name="14 Any headers (mọi ngôn ngữ)" sheetId="14" r:id="rId14"/>
+    <sheet name="15 Finished deck (hoàn chỉnh)" sheetId="15" r:id="rId15"/>
   </sheets>
 </workbook>
 </file>
@@ -211,7 +210,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">size=40; tts=zh_CN</t>
+          <t xml:space="preserve">size=40; tts=zh_CN; voices=Ting-Ting,Microsoft Huihui</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2514,794 +2513,689 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYNC</t>
+          <t xml:space="preserve">SUBDECK 1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUBDECK 1</t>
+          <t xml:space="preserve">SUBDECK 2</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUBDECK 2</t>
+          <t xml:space="preserve">SUBDECK 3</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUBDECK 3</t>
+          <t xml:space="preserve">TAGS</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAGS</t>
+          <t xml:space="preserve">Japanese</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Picture</t>
+          <t xml:space="preserve">Meaning</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Word</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pinyin</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meaning</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
           <t xml:space="preserve">Example</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recording</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clip</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Source</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">#config align=left; speed=0.9; reverse; theme=sakura</t>
+          <t xml:space="preserve">#config theme=sakura</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">size=40; furigana; tts=ja_JP</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">image; size=260; label=Look</t>
+          <t xml:space="preserve">side=back; size=22</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">side=front; size=44; bold; tts=zh_CN; voices=Ting-Ting,Microsoft Huihui</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=back; size=22; color=accent; align=center; type=nc</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=back; size=20</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=back; size=16; color=muted; italic; tts=zh_CN; speed=0.7</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=back; audio; label=Native recording</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=back; video; size=480; hint; label=Watch</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=hide</t>
+          <t xml:space="preserve">side=back; size=16; color=muted; italic; furigana</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">e01</t>
+          <t xml:space="preserve">n01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">JLPT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Places</t>
+          <t xml:space="preserve">N5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Verbs</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cities</t>
+          <t xml:space="preserve">jlpt, n5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cities, hsk1</t>
+          <t xml:space="preserve">食[た]べる</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/f/fa/Great_Wall_of_China_July_2006.JPG/500px-Great_Wall_of_China_July_2006.JPG</t>
+          <t xml:space="preserve">ăn</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">北京</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Běijīng</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bắc Kinh, thủ đô</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">北京有很多名胜古迹。</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/8/8a/Zh-Beijing.ogg</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.youtube.com/watch?v=jNQXAC9IVRw</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">internal note, never shown</t>
+          <t xml:space="preserve">朝[あさ]ごはんを 食[た]べます。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">e02</t>
+          <t xml:space="preserve">n02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">JLPT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Places</t>
+          <t xml:space="preserve">N5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Verbs</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cities</t>
+          <t xml:space="preserve">jlpt, n5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">cities</t>
+          <t xml:space="preserve">飲[の]む</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uống</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">上海</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shànghǎi</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thượng Hải, thành phố lớn nhất</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">上海在长江的入海口。</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/73/Zh-Shanghai.ogg</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">internal note, never shown</t>
+          <t xml:space="preserve">毎朝[まいあさ] コーヒーを 飲[の]みます。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">e03</t>
+          <t xml:space="preserve">n03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">JLPT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Places</t>
+          <t xml:space="preserve">N5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Verbs</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cities</t>
+          <t xml:space="preserve">jlpt, n5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">cities</t>
+          <t xml:space="preserve">行[い]く</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">đi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">广州</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Guǎngzhōu</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quảng Châu</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">广州的早茶很有名。</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/8/82/Zh-Guangzhou.ogg</t>
+          <t xml:space="preserve">来週[らいしゅう] 京都[きょうと]へ 行[い]きます。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">e04</t>
+          <t xml:space="preserve">n04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">JLPT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Places</t>
+          <t xml:space="preserve">N5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Verbs</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cities</t>
+          <t xml:space="preserve">jlpt, n5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">cities</t>
+          <t xml:space="preserve">話[はな]す</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nói chuyện</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">杭州</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hángzhōu</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hàng Châu</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">杭州有西湖。</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/3/36/Zh-Hangzhou.ogg</t>
+          <t xml:space="preserve">日本語[にほんご]で 話[はな]しましょう。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">e05</t>
+          <t xml:space="preserve">n05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">JLPT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Places</t>
+          <t xml:space="preserve">N5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Nouns</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provinces</t>
+          <t xml:space="preserve">jlpt, n5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">provinces</t>
+          <t xml:space="preserve">学校[がっこう]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Mount_Everest_as_seen_from_Drukair2_PLW_edit.jpg/500px-Mount_Everest_as_seen_from_Drukair2_PLW_edit.jpg</t>
+          <t xml:space="preserve">trường học</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">安徽</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ānhuī</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tỉnh An Huy</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">安徽有黄山。</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/5/57/Zh-Anhui.ogg</t>
+          <t xml:space="preserve">学校[がっこう]は 駅[えき]の 近[ちか]くです。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">e06</t>
+          <t xml:space="preserve">n06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">JLPT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Places</t>
+          <t xml:space="preserve">N5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Nouns</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">History</t>
+          <t xml:space="preserve">jlpt, n5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">友[とも]だち</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Terracotta_Army_Pit_1_-_2.jpg/500px-Terracotta_Army_Pit_1_-_2.jpg</t>
+          <t xml:space="preserve">bạn bè</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">长安</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cháng'ān</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trường An, kinh đô thời Đường</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">长安是今天的西安。</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/9/9e/Zh-Changan.ogg</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://youtu.be/aircAruvnKk</t>
+          <t xml:space="preserve">友[とも]だちと 映画[えいが]を 見[み]ました。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">e07</t>
+          <t xml:space="preserve">n07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t xml:space="preserve">JLPT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Places</t>
+          <t xml:space="preserve">N5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Nouns</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cities</t>
+          <t xml:space="preserve">jlpt, n5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">cities</t>
+          <t xml:space="preserve">電車[でんしゃ]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tàu điện</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">天津</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiānjīn</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thiên Tân — dòng này đang tắt nên không bao giờ vào Anki</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">天津在北京的东边。</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/9/9b/Zh-Tianjin.ogg</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SYNC</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Word</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meaning</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Picture</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clip</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sentence</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Extra</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#config align=middle; spid=3; reverse; theme=neon</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">size=400; colour=red; tts=zh; cloze</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=upside; cloze</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">image; audio; tts=en_US; bold; size=5000; furigana</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">video; size=9000</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">speed=3; label</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">size=abc; align; subdeck=1; bold</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">size=20</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">x01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{c1::重复}}的表头</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duplicated header — only the first 'Meaning' is a field</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/36/Green_tea_3_appearances.jpg/500px-Green_tea_3_appearances.jpg</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.youtube.com/@nationalgeographic</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A channel link is not a video: it is passed through with a warning.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">this cell is ignored</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">x02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{c1::网盘}}链接</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a Google Drive link is rewritten to its /preview player</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://drive.google.com/file/d/1PLACEHOLDER_FILE_ID_HERE/view</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The id here is a placeholder, so the frame will not play anything.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{c1::无编号}}的一行</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a row with no ID is counted and skipped</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nothing is written to Anki for it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">x01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{c1::重复}}的编号</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the same ID twice — the sync reports it</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two rows cannot key one note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">x05</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{c1::关闭}}的一行</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">switched off</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not marked for sync, so it is skipped.</t>
+          <t xml:space="preserve">電車[でんしゃ]で 会社[かいしゃ]へ 行[い]きます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JLPT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N5</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nouns</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jlpt, n5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">時間[じかん]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thời gian</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">今日[きょう]は 時間[じかん]が ありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JLPT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjectives</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jlpt, n5</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新[あたら]しい</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mới</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新[あたら]しい 本[ほん]を 買[か]いました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JLPT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjectives</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jlpt, n5</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高[たか]い</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cao; đắt</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">この 店[みせ]は 少[すこ]し 高[たか]いです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JLPT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N5</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjectives</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jlpt, n5</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">静[しず]か</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yên tĩnh</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">この 部屋[へや]は とても 静[しず]かです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JLPT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N4</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verbs</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jlpt, n4</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">調[しら]べる</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tra cứu; tìm hiểu</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辞書[じしょ]で 言葉[ことば]を 調[しら]べます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JLPT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verbs</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jlpt, n4</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">続[つづ]ける</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tiếp tục</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">毎日[まいにち] 練習[れんしゅう]を 続[つづ]けます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JLPT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N4</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nouns</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jlpt, n4</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">季節[きせつ]</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mùa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日本[にほん]には 四[よっ]つの 季節[きせつ]が あります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JLPT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nouns</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jlpt, n4</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">桜[さくら]</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hoa anh đào</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">春[はる]に 桜[さくら]が 咲[さ]きます。</t>
         </is>
       </c>
     </row>

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -2149,7 +2149,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">size=40; furigana</t>
+          <t xml:space="preserve">size=40; furigana; tts=ja_JP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -16,7 +16,7 @@
     <sheet name="12 Chinese drawing (viết tay)" sheetId="12" r:id="rId12"/>
     <sheet name="13 Furigana (phiên âm kanji)" sheetId="13" r:id="rId13"/>
     <sheet name="14 Any headers (mọi ngôn ngữ)" sheetId="14" r:id="rId14"/>
-    <sheet name="15 Finished deck (hoàn chỉnh)" sheetId="15" r:id="rId15"/>
+    <sheet name="15 Theme + subdeck (màu, tầng)" sheetId="15" r:id="rId15"/>
   </sheets>
 </workbook>
 </file>

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -17,6 +17,11 @@
     <sheet name="13 Furigana (phiên âm kanji)" sheetId="13" r:id="rId13"/>
     <sheet name="14 Any headers (mọi ngôn ngữ)" sheetId="14" r:id="rId14"/>
     <sheet name="15 Theme + subdeck (màu, tầng)" sheetId="15" r:id="rId15"/>
+    <sheet name="16 Picture words (từ vựng ảnh)" sheetId="16" r:id="rId16"/>
+    <sheet name="17 Draw &amp; type (viết và gõ)" sheetId="17" r:id="rId17"/>
+    <sheet name="18 Grammar cloze (ngữ pháp)" sheetId="18" r:id="rId18"/>
+    <sheet name="19 Dictation (nghe rồi gõ)" sheetId="19" r:id="rId19"/>
+    <sheet name="20 Video lesson (bài video)" sheetId="20" r:id="rId20"/>
   </sheets>
 </workbook>
 </file>
@@ -3203,6 +3208,1270 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Group</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Picture</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Word</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sound</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meaning</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subdeck=1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; image; size=300</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=44; bold</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; audio; label=Native recording</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=16; color=muted; italic; hint</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animals</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Cat_November_2010-1a.jpg/500px-Cat_November_2010-1a.jpg</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cat</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-cat.ogg</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">con mèo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The cat is asleep on the chair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animals</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/3c/Giant_Panda_2004-03-2.jpg/500px-Giant_Panda_2004-03-2.jpg</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">panda</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-panda.ogg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gấu trúc</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pandas eat bamboo almost all day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animals</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/17/Tiger_in_Ranthambhore.jpg/500px-Tiger_in_Ranthambhore.jpg</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tiger</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-tiger.ogg</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">con hổ</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A tiger hunts alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animals</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/9/98/Horse-and-pony.jpg/500px-Horse-and-pony.jpg</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">horse</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-horse.ogg</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">con ngựa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She rides a horse every weekend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Food and drink</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/15/Red_Apple.jpg/500px-Red_Apple.jpg</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">apple</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-apple.ogg</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quả táo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An apple a day is an old English saying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Food and drink</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/36/Green_tea_3_appearances.jpg/500px-Green_tea_3_appearances.jpg</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tea</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-tea.ogg</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trà</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Green tea is drunk without milk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nature</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/Full_Moon_Luc_Viatour.jpg/500px-Full_Moon_Luc_Viatour.jpg</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moon</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-moon.ogg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mặt trăng</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The moon is full tonight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nature</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Fire.JPG/500px-Fire.JPG</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-fire.ogg</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lửa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">They built a fire on the beach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nature</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Mount_Everest_as_seen_from_Drukair2_PLW_edit.jpg/500px-Mount_Everest_as_seen_from_Drukair2_PLW_edit.jpg</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mountain</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-mountain.ogg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ngọn núi</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The mountain is covered in snow.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Level</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meaning</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Draw</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pinyin</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Character</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subdeck=1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; size=26; color=muted; label=Draw it, then type the pinyin</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; draw; size=240</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=26; color=accent; type=nc</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=64; tts=zh_CN</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=16; color=muted; italic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSK 1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sách</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">书</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shū</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">书</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我在看书。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSK 1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cơm; bữa ăn</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">饭</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fàn</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">饭</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">该吃饭了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSK 1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nhà</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">家</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jiā</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">家</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我在家工作。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSK 1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nói</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shuō</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">请说慢一点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSK 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nghe</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">听</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tīng</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">听</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我在听音乐。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSK 2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">đường phố</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">路</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lù</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">路</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">这条路很长。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSK 2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trà</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">茶</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chá</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">茶</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我想喝茶。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSK 2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mưa</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雨</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yǔ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雨</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">今天下雨了。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Point</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sentence</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meaning</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; size=15; color=muted; label=Grammar point</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cloze; type; size=28</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=15; color=muted; hint</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comparison</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">他{{c1::比}}我高。</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anh ấy cao hơn tôi.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">比 compares two things: A 比 B + adjective.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Completed action</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我{{c1::了}}买三本书。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tôi đã mua ba quyển sách.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">了 after the verb marks the action as completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Experience</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我去{{c1::过}}北京。</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tôi từng đến Bắc Kinh.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">过 says it happened at least once, ever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ability</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">她{{c1::会}}开车。</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cô ấy biết lái xe.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">会 is a learned skill; 能 is being able to right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progressive</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">他{{c1::在}}打电话。</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anh ấy đang gọi điện.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在 before the verb makes it in progress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Passive</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杯子{{c1::被}}弟弟打破了。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cái cốc bị em trai làm vỡ.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">被 introduces the doer, like the English passive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duration</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我学了{{c1::两年}}中文。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tôi học tiếng Trung hai năm rồi.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duration comes after the verb, not before it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sentence</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pinyin</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=hide; tts=zh_CN; speed=0.85; type</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; size=18; color=muted</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20; color=accent</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我叫王小明。</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listen, then type the sentence in Chinese.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wǒ jiào Wáng Xiǎomíng.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tôi tên là Vương Tiểu Minh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">今天天气很好。</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listen, then type the sentence in Chinese.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jīntiān tiānqì hěn hǎo.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hôm nay thời tiết rất đẹp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我想喝一杯咖啡。</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listen, then type the sentence in Chinese.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wǒ xiǎng hē yì bēi kāfēi.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tôi muốn uống một tách cà phê.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">这本书是我的。</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listen, then type the sentence in Chinese.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zhè běn shū shì wǒ de.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quyển sách này là của tôi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">他每天坐地铁上班。</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listen, then type the sentence in Chinese.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tā měitiān zuò dìtiě shàngbān.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anh ấy đi làm bằng tàu điện ngầm mỗi ngày.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">请问洗手间在哪儿？</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listen, then type the sentence in Chinese.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qǐngwèn xǐshǒujiān zài nǎr?</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cho hỏi nhà vệ sinh ở đâu?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
@@ -3506,6 +4775,148 @@
       <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">Same as 'no'.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesson</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clip</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subdeck=1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; video; size=520</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; size=22</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesson 1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/watch?v=jNQXAC9IVRw</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Where are the speakers standing?</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In front of the elephant enclosure at the zoo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesson 1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://youtu.be/aircAruvnKk</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What is the subject of this lecture?</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How a neural network is put together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesson 2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/d/de/Ink_grinding.webmhd.webm</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What is being ground on the stone?</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An ink stick, ground with water to make ink.</t>
         </is>
       </c>
     </row>

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -188,12 +188,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chinese</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pinyin</t>
+          <t xml:space="preserve">Phonetic</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">size=40; tts=zh_CN; voices=Ting-Ting,Microsoft Huihui</t>
+          <t xml:space="preserve">size=34; tts=en_US; voices=Samantha,Microsoft Zira</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -230,7 +230,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">side=hide; tts=zh_CN; speed=0.5</t>
+          <t xml:space="preserve">side=hide; tts=en_US; speed=0.5</t>
         </is>
       </c>
     </row>
@@ -242,12 +242,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">早上好</t>
+          <t xml:space="preserve">Good morning.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">zǎoshang hǎo</t>
+          <t xml:space="preserve">/ɡʊd ˈmɔːnɪŋ/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -257,7 +257,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">早上好</t>
+          <t xml:space="preserve">Good morning.</t>
         </is>
       </c>
     </row>
@@ -269,12 +269,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">谢谢你的帮助</t>
+          <t xml:space="preserve">Thank you for your help.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">xièxie nǐ de bāngzhù</t>
+          <t xml:space="preserve">/θæŋk juː fə jɔː help/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -284,7 +284,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">谢谢你的帮助</t>
+          <t xml:space="preserve">Thank you for your help.</t>
         </is>
       </c>
     </row>
@@ -296,22 +296,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">请再说一遍</t>
+          <t xml:space="preserve">Could you say that again?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">qǐng zài shuō yí biàn</t>
+          <t xml:space="preserve">/kʊd juː seɪ ðæt əˈɡen/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">làm ơn nói lại một lần nữa</t>
+          <t xml:space="preserve">bạn nói lại được không?</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">请再说一遍</t>
+          <t xml:space="preserve">Could you say that again?</t>
         </is>
       </c>
     </row>
@@ -323,22 +323,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">我听不懂</t>
+          <t xml:space="preserve">I do not understand.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">wǒ tīng bu dǒng</t>
+          <t xml:space="preserve">/aɪ duː nɒt ˌʌndəˈstænd/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">tôi nghe không hiểu</t>
+          <t xml:space="preserve">tôi không hiểu</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">我听不懂</t>
+          <t xml:space="preserve">I do not understand.</t>
         </is>
       </c>
     </row>
@@ -350,22 +350,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">多少钱</t>
+          <t xml:space="preserve">How much is it?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">duōshao qián</t>
+          <t xml:space="preserve">/haʊ mʌtʃ ɪz ɪt/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">bao nhiêu tiền</t>
+          <t xml:space="preserve">cái này bao nhiêu tiền?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">多少钱</t>
+          <t xml:space="preserve">How much is it?</t>
         </is>
       </c>
     </row>
@@ -377,22 +377,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">洗手间在哪儿</t>
+          <t xml:space="preserve">Where is the bathroom?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">xǐshǒujiān zài nǎr</t>
+          <t xml:space="preserve">/weər ɪz ðə ˈbɑːθruːm/</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">nhà vệ sinh ở đâu</t>
+          <t xml:space="preserve">nhà vệ sinh ở đâu?</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">洗手间在哪儿</t>
+          <t xml:space="preserve">Where is the bathroom?</t>
         </is>
       </c>
     </row>
@@ -3335,27 +3335,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/3c/Giant_Panda_2004-03-2.jpg/500px-Giant_Panda_2004-03-2.jpg</t>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/17/Tiger_in_Ranthambhore.jpg/500px-Tiger_in_Ranthambhore.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">panda</t>
+          <t xml:space="preserve">tiger</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-panda.ogg</t>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-tiger.ogg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gấu trúc</t>
+          <t xml:space="preserve">con hổ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pandas eat bamboo almost all day.</t>
+          <t xml:space="preserve">A tiger hunts alone.</t>
         </is>
       </c>
     </row>
@@ -3372,27 +3372,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/17/Tiger_in_Ranthambhore.jpg/500px-Tiger_in_Ranthambhore.jpg</t>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/9/98/Horse-and-pony.jpg/500px-Horse-and-pony.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">tiger</t>
+          <t xml:space="preserve">horse</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-tiger.ogg</t>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-horse.ogg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">con hổ</t>
+          <t xml:space="preserve">con ngựa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A tiger hunts alone.</t>
+          <t xml:space="preserve">She rides a horse every weekend.</t>
         </is>
       </c>
     </row>
@@ -3404,32 +3404,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Animals</t>
+          <t xml:space="preserve">Food and drink</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/9/98/Horse-and-pony.jpg/500px-Horse-and-pony.jpg</t>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/15/Red_Apple.jpg/500px-Red_Apple.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">horse</t>
+          <t xml:space="preserve">apple</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-horse.ogg</t>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-apple.ogg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">con ngựa</t>
+          <t xml:space="preserve">quả táo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">She rides a horse every weekend.</t>
+          <t xml:space="preserve">An apple a day is an old English saying.</t>
         </is>
       </c>
     </row>
@@ -3441,32 +3441,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Food and drink</t>
+          <t xml:space="preserve">Nature</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/15/Red_Apple.jpg/500px-Red_Apple.jpg</t>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/Full_Moon_Luc_Viatour.jpg/500px-Full_Moon_Luc_Viatour.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">apple</t>
+          <t xml:space="preserve">moon</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-apple.ogg</t>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-moon.ogg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">quả táo</t>
+          <t xml:space="preserve">mặt trăng</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">An apple a day is an old English saying.</t>
+          <t xml:space="preserve">The moon is full tonight.</t>
         </is>
       </c>
     </row>
@@ -3478,143 +3478,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Food and drink</t>
+          <t xml:space="preserve">Nature</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/36/Green_tea_3_appearances.jpg/500px-Green_tea_3_appearances.jpg</t>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Fire.JPG/500px-Fire.JPG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tea</t>
+          <t xml:space="preserve">fire</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-tea.ogg</t>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-fire.ogg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">trà</t>
+          <t xml:space="preserve">lửa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green tea is drunk without milk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">i07</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nature</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/Full_Moon_Luc_Viatour.jpg/500px-Full_Moon_Luc_Viatour.jpg</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">moon</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-moon.ogg</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mặt trăng</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The moon is full tonight.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">i08</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nature</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Fire.JPG/500px-Fire.JPG</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fire</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-fire.ogg</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lửa</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
           <t xml:space="preserve">They built a fire on the beach.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">i09</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nature</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Mount_Everest_as_seen_from_Drukair2_PLW_edit.jpg/500px-Mount_Everest_as_seen_from_Drukair2_PLW_edit.jpg</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mountain</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-mountain.ogg</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ngọn núi</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The mountain is covered in snow.</t>
         </is>
       </c>
     </row>
@@ -4064,22 +3953,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comparison</t>
+          <t xml:space="preserve">Present perfect</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">他{{c1::比}}我高。</t>
+          <t xml:space="preserve">I have {{c1::lived}} in this city since 2019.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anh ấy cao hơn tôi.</t>
+          <t xml:space="preserve">Tôi sống ở thành phố này từ năm 2019.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">比 compares two things: A 比 B + adjective.</t>
+          <t xml:space="preserve">since + a point in time; for + a length of time.</t>
         </is>
       </c>
     </row>
@@ -4091,22 +3980,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Completed action</t>
+          <t xml:space="preserve">Articles</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">我{{c1::了}}买三本书。</t>
+          <t xml:space="preserve">She plays {{c1::the}} piano every evening.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tôi đã mua ba quyển sách.</t>
+          <t xml:space="preserve">Tối nào cô ấy cũng chơi piano.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">了 after the verb marks the action as completed.</t>
+          <t xml:space="preserve">Instruments take the; sports take nothing at all.</t>
         </is>
       </c>
     </row>
@@ -4118,22 +4007,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Experience</t>
+          <t xml:space="preserve">Comparatives</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">我去{{c1::过}}北京。</t>
+          <t xml:space="preserve">Today is {{c1::hotter}} than yesterday.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tôi từng đến Bắc Kinh.</t>
+          <t xml:space="preserve">Hôm nay nóng hơn hôm qua.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">过 says it happened at least once, ever.</t>
+          <t xml:space="preserve">Short adjectives take -er, and the consonant doubles.</t>
         </is>
       </c>
     </row>
@@ -4145,22 +4034,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ability</t>
+          <t xml:space="preserve">Passive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">她{{c1::会}}开车。</t>
+          <t xml:space="preserve">The bridge {{c1::was}} built in 1890.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cô ấy biết lái xe.</t>
+          <t xml:space="preserve">Cây cầu được xây năm 1890.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">会 is a learned skill; 能 is being able to right now.</t>
+          <t xml:space="preserve">be + past participle, when who did it does not matter.</t>
         </is>
       </c>
     </row>
@@ -4172,22 +4061,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progressive</t>
+          <t xml:space="preserve">Reported speech</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">他{{c1::在}}打电话。</t>
+          <t xml:space="preserve">He said he {{c1::was}} tired.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anh ấy đang gọi điện.</t>
+          <t xml:space="preserve">Anh ấy nói anh ấy mệt.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">在 before the verb makes it in progress.</t>
+          <t xml:space="preserve">The tense steps back one when the sentence is reported.</t>
         </is>
       </c>
     </row>
@@ -4199,22 +4088,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passive</t>
+          <t xml:space="preserve">Prepositions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">杯子{{c1::被}}弟弟打破了。</t>
+          <t xml:space="preserve">We arrived {{c1::at}} the station at six.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cái cốc bị em trai làm vỡ.</t>
+          <t xml:space="preserve">Chúng tôi đến ga lúc sáu giờ.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">被 introduces the doer, like the English passive.</t>
+          <t xml:space="preserve">arrive at a place, arrive in a city or a country.</t>
         </is>
       </c>
     </row>
@@ -4226,22 +4115,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration</t>
+          <t xml:space="preserve">Used to</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">我学了{{c1::两年}}中文。</t>
+          <t xml:space="preserve">There {{c1::used}} to be a cinema on this corner.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tôi học tiếng Trung hai năm rồi.</t>
+          <t xml:space="preserve">Ở góc này trước kia có một rạp chiếu phim.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duration comes after the verb, not before it.</t>
+          <t xml:space="preserve">For something that was true once and is not now.</t>
         </is>
       </c>
     </row>
@@ -4270,11 +4159,6 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pinyin</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t xml:space="preserve">Meaning</t>
         </is>
       </c>
@@ -4287,7 +4171,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">side=hide; tts=zh_CN; speed=0.85; type</t>
+          <t xml:space="preserve">side=hide; tts=en_US; speed=0.85; type</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4296,11 +4180,6 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=back; size=20; color=accent</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">side=back; size=20</t>
         </is>
@@ -4314,22 +4193,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">我叫王小明。</t>
+          <t xml:space="preserve">My name is Mai and I live in Hanoi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Listen, then type the sentence in Chinese.</t>
+          <t xml:space="preserve">Listen, then type the sentence in English.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wǒ jiào Wáng Xiǎomíng.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tôi tên là Vương Tiểu Minh.</t>
+          <t xml:space="preserve">Tôi tên là Mai và tôi sống ở Hà Nội.</t>
         </is>
       </c>
     </row>
@@ -4341,20 +4215,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">今天天气很好。</t>
+          <t xml:space="preserve">The weather is very nice today</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Listen, then type the sentence in Chinese.</t>
+          <t xml:space="preserve">Listen, then type the sentence in English.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jīntiān tiānqì hěn hǎo.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">Hôm nay thời tiết rất đẹp.</t>
         </is>
@@ -4368,22 +4237,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">我想喝一杯咖啡。</t>
+          <t xml:space="preserve">I would like a cup of coffee please</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Listen, then type the sentence in Chinese.</t>
+          <t xml:space="preserve">Listen, then type the sentence in English.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wǒ xiǎng hē yì bēi kāfēi.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tôi muốn uống một tách cà phê.</t>
+          <t xml:space="preserve">Cho tôi một tách cà phê.</t>
         </is>
       </c>
     </row>
@@ -4395,22 +4259,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">这本书是我的。</t>
+          <t xml:space="preserve">This book belongs to my sister</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Listen, then type the sentence in Chinese.</t>
+          <t xml:space="preserve">Listen, then type the sentence in English.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhè běn shū shì wǒ de.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quyển sách này là của tôi.</t>
+          <t xml:space="preserve">Quyển sách này là của chị tôi.</t>
         </is>
       </c>
     </row>
@@ -4422,22 +4281,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">他每天坐地铁上班。</t>
+          <t xml:space="preserve">He takes the train to work every morning</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Listen, then type the sentence in Chinese.</t>
+          <t xml:space="preserve">Listen, then type the sentence in English.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tā měitiān zuò dìtiě shàngbān.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anh ấy đi làm bằng tàu điện ngầm mỗi ngày.</t>
+          <t xml:space="preserve">Sáng nào anh ấy cũng đi làm bằng tàu.</t>
         </is>
       </c>
     </row>
@@ -4449,22 +4303,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">请问洗手间在哪儿？</t>
+          <t xml:space="preserve">Could you tell me where the station is</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Listen, then type the sentence in Chinese.</t>
+          <t xml:space="preserve">Listen, then type the sentence in English.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qǐngwèn xǐshǒujiān zài nǎr?</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cho hỏi nhà vệ sinh ở đâu?</t>
+          <t xml:space="preserve">Bạn chỉ giúp tôi ga ở đâu được không?</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4789,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pinyin</t>
+          <t xml:space="preserve">Phonetic</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5009,12 +4858,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">图书馆</t>
+          <t xml:space="preserve">library</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">túshūguǎn</t>
+          <t xml:space="preserve">/ˈlaɪbrəri/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5024,17 +4873,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">图书馆在学校旁边。</t>
+          <t xml:space="preserve">The library is next to the school.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Literally “book-store-hall”.</t>
+          <t xml:space="preserve">British speakers often say it in two syllables.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HSK 3 word list</t>
+          <t xml:space="preserve">Oxford 3000</t>
         </is>
       </c>
     </row>
@@ -5046,32 +4895,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞机</t>
+          <t xml:space="preserve">airport</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fēijī</t>
+          <t xml:space="preserve">/ˈeəpɔːt/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">máy bay</t>
+          <t xml:space="preserve">sân bay</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">我明天坐飞机去上海。</t>
+          <t xml:space="preserve">We got to the airport two hours early.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">飞 = to fly, 机 = machine.</t>
+          <t xml:space="preserve">air + port, the way most compound nouns are built.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HSK 1 word list</t>
+          <t xml:space="preserve">Oxford 3000</t>
         </is>
       </c>
     </row>
@@ -5083,12 +4932,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">hospital</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">yīyuàn</t>
+          <t xml:space="preserve">/ˈhɒspɪtl/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5098,17 +4947,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">他在医院工作。</t>
+          <t xml:space="preserve">She works at a hospital downtown.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">医 = to heal, 院 = courtyard.</t>
+          <t xml:space="preserve">In British English: in hospital, no article.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HSK 1 word list</t>
+          <t xml:space="preserve">Oxford 3000</t>
         </is>
       </c>
     </row>
@@ -5120,12 +4969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">季节</t>
+          <t xml:space="preserve">season</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">jìjié</t>
+          <t xml:space="preserve">/ˈsiːzn/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5135,17 +4984,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">北京的四个季节都很清楚。</t>
+          <t xml:space="preserve">Autumn is my favourite season.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Used for seasons of the year only.</t>
+          <t xml:space="preserve">Also a verb: to season food.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HSK 3 word list</t>
+          <t xml:space="preserve">Oxford 3000</t>
         </is>
       </c>
     </row>
@@ -5157,32 +5006,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">习惯</t>
+          <t xml:space="preserve">habit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">xíguàn</t>
+          <t xml:space="preserve">/ˈhæbɪt/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">thói quen; quen với</t>
+          <t xml:space="preserve">thói quen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">我习惯早起。</t>
+          <t xml:space="preserve">Reading before bed is a good habit.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Works as both noun and verb.</t>
+          <t xml:space="preserve">A habit is repeated; a custom is shared by a group.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HSK 3 word list</t>
+          <t xml:space="preserve">Oxford 3000</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5043,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">环境</t>
+          <t xml:space="preserve">environment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">huánjìng</t>
+          <t xml:space="preserve">/ɪnˈvaɪrənmənt/</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5209,17 +5058,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">这里的环境很安静。</t>
+          <t xml:space="preserve">The environment here is very quiet.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Covers surroundings, not only nature.</t>
+          <t xml:space="preserve">Covers surroundings in general, not only nature.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HSK 3 word list</t>
+          <t xml:space="preserve">Oxford 3000</t>
         </is>
       </c>
     </row>
@@ -5243,12 +5092,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chinese</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pinyin</t>
+          <t xml:space="preserve">Phonetic</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5136,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">读</t>
+          <t xml:space="preserve">to read</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">dú</t>
+          <t xml:space="preserve">/riːd/</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5158,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">写</t>
+          <t xml:space="preserve">to write</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">xiě</t>
+          <t xml:space="preserve">/raɪt/</t>
         </is>
       </c>
     </row>
@@ -5331,12 +5180,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">听</t>
+          <t xml:space="preserve">to listen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">tīng</t>
+          <t xml:space="preserve">/ˈlɪsn/</t>
         </is>
       </c>
     </row>
@@ -5353,12 +5202,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">说</t>
+          <t xml:space="preserve">to speak</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">shuō</t>
+          <t xml:space="preserve">/spiːk/</t>
         </is>
       </c>
     </row>
@@ -5375,12 +5224,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">记得</t>
+          <t xml:space="preserve">to remember</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">jìde</t>
+          <t xml:space="preserve">/rɪˈmembə/</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5246,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">忘记</t>
+          <t xml:space="preserve">to forget</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">wàngjì</t>
+          <t xml:space="preserve">/fəˈɡet/</t>
         </is>
       </c>
     </row>
@@ -5421,12 +5270,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t xml:space="preserve">English</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vietnamese</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spanish</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5465,17 +5314,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t xml:space="preserve">the tree</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t xml:space="preserve">cái cây</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el árbol</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">type=nc ignores the accent, so “el arbol” counts.</t>
+          <t xml:space="preserve">type=nc ignores the marks, so “cai cay” is counted right.</t>
         </is>
       </c>
     </row>
@@ -5487,12 +5336,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t xml:space="preserve">the city</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t xml:space="preserve">thành phố</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la ciudad</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5353,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t xml:space="preserve">the heart</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t xml:space="preserve">trái tim</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el corazón</t>
         </is>
       </c>
     </row>
@@ -5521,12 +5370,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t xml:space="preserve">quickly</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t xml:space="preserve">nhanh chóng</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rápidamente</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5387,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t xml:space="preserve">the bird</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t xml:space="preserve">con chim</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el pájaro</t>
         </is>
       </c>
     </row>
@@ -5555,12 +5404,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t xml:space="preserve">the moon</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t xml:space="preserve">mặt trăng</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la luna</t>
         </is>
       </c>
     </row>
@@ -5572,17 +5421,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t xml:space="preserve">the mountain</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t xml:space="preserve">ngọn núi</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la montaña</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ñ is a letter, not an accent — it must be typed.</t>
+          <t xml:space="preserve">Marks are ignored, letters are not: đ is a letter and must be typed.</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5443,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t xml:space="preserve">the river</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t xml:space="preserve">con sông</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el río</t>
         </is>
       </c>
     </row>
@@ -5623,15 +5472,10 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pinyin</t>
+          <t xml:space="preserve">Meaning</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Translation</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
         <is>
           <t xml:space="preserve">Note</t>
         </is>
@@ -5645,20 +5489,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cloze; size=30</t>
+          <t xml:space="preserve">cloze; size=28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">size=18; color=accent</t>
+          <t xml:space="preserve">size=18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">size=18</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">size=14; color=muted; hint</t>
         </is>
@@ -5672,22 +5511,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">我{{c1::是}}中国人。</t>
+          <t xml:space="preserve">She has {{c1::been}} living here for ten years.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wǒ shì Zhōngguórén.</t>
+          <t xml:space="preserve">Cô ấy sống ở đây mười năm rồi.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tôi là người Trung Quốc.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">是 links two nouns; it is not used before an adjective.</t>
+          <t xml:space="preserve">Present perfect continuous: has been + -ing.</t>
         </is>
       </c>
     </row>
@@ -5699,20 +5533,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">他{{c1::在}}图书馆{{c2::看}}书。</t>
+          <t xml:space="preserve">I {{c1::have}} never been to Japan, and neither {{c2::has}} she.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tā zài túshūguǎn kàn shū.</t>
+          <t xml:space="preserve">Tôi chưa từng đến Nhật, cô ấy cũng vậy.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anh ấy đang đọc sách trong thư viện.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">Two deletions make two cards from one row.</t>
         </is>
@@ -5726,22 +5555,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">我们{{c1::明天}}去北京。</t>
+          <t xml:space="preserve">The letter was written {{c1::by}} my grandmother.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wǒmen míngtiān qù Běijīng.</t>
+          <t xml:space="preserve">Bức thư do bà tôi viết.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngày mai chúng tôi đi Bắc Kinh.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time words come before the verb.</t>
+          <t xml:space="preserve">In the passive, by introduces who did it.</t>
         </is>
       </c>
     </row>
@@ -5753,22 +5577,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">这本书{{c1::很}}有意思。</t>
+          <t xml:space="preserve">If it rains, we {{c1::will}} stay at home.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhè běn shū hěn yǒuyìsi.</t>
+          <t xml:space="preserve">Nếu trời mưa thì chúng tôi ở nhà.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quyển sách này rất thú vị.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">很 is required before a bare adjective.</t>
+          <t xml:space="preserve">First conditional: if + present, will + verb.</t>
         </is>
       </c>
     </row>
@@ -5780,22 +5599,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">她{{c1::会}}说三种语言。</t>
+          <t xml:space="preserve">This film is {{c1::more}} interesting than the last one.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tā huì shuō sān zhǒng yǔyán.</t>
+          <t xml:space="preserve">Phim này hay hơn phim trước.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cô ấy nói được ba thứ tiếng.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">会 is learned ability.</t>
+          <t xml:space="preserve">Long adjectives take more, not -er.</t>
         </is>
       </c>
     </row>
@@ -5807,22 +5621,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">请{{c1::把}}门关上。</t>
+          <t xml:space="preserve">I used {{c1::to}} walk to school every day.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qǐng bǎ mén guānshàng.</t>
+          <t xml:space="preserve">Hồi trước ngày nào tôi cũng đi bộ đến trường.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Làm ơn đóng cửa lại.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">把 moves the object in front of the verb.</t>
+          <t xml:space="preserve">used to + bare verb, for a past habit that stopped.</t>
         </is>
       </c>
     </row>
@@ -5895,22 +5704,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Cat_November_2010-1a.jpg/500px-Cat_November_2010-1a.jpg</t>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/3c/Giant_Panda_2004-03-2.jpg/500px-Giant_Panda_2004-03-2.jpg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">猫</t>
+          <t xml:space="preserve">熊猫</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">māo</t>
+          <t xml:space="preserve">xióngmāo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">con mèo</t>
+          <t xml:space="preserve">gấu trúc</t>
         </is>
       </c>
     </row>
@@ -5922,22 +5731,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/3c/Giant_Panda_2004-03-2.jpg/500px-Giant_Panda_2004-03-2.jpg</t>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/36/Green_tea_3_appearances.jpg/500px-Green_tea_3_appearances.jpg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">熊猫</t>
+          <t xml:space="preserve">茶</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">xióngmāo</t>
+          <t xml:space="preserve">chá</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gấu trúc</t>
+          <t xml:space="preserve">trà</t>
         </is>
       </c>
     </row>
@@ -5949,22 +5758,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/3/36/Green_tea_3_appearances.jpg/500px-Green_tea_3_appearances.jpg</t>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/f/fa/Great_Wall_of_China_July_2006.JPG/500px-Great_Wall_of_China_July_2006.JPG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">茶</t>
+          <t xml:space="preserve">长城</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">chá</t>
+          <t xml:space="preserve">Chángchéng</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">trà</t>
+          <t xml:space="preserve">Vạn Lý Trường Thành</t>
         </is>
       </c>
     </row>
@@ -5976,22 +5785,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/f/fa/Great_Wall_of_China_July_2006.JPG/500px-Great_Wall_of_China_July_2006.JPG</t>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Terracotta_Army_Pit_1_-_2.jpg/500px-Terracotta_Army_Pit_1_-_2.jpg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">长城</t>
+          <t xml:space="preserve">兵马俑</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chángchéng</t>
+          <t xml:space="preserve">bīngmǎyǒng</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vạn Lý Trường Thành</t>
+          <t xml:space="preserve">đội quân đất nung</t>
         </is>
       </c>
     </row>
@@ -6003,182 +5812,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Terracotta_Army_Pit_1_-_2.jpg/500px-Terracotta_Army_Pit_1_-_2.jpg</t>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Mount_Everest_as_seen_from_Drukair2_PLW_edit.jpg/500px-Mount_Everest_as_seen_from_Drukair2_PLW_edit.jpg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">兵马俑</t>
+          <t xml:space="preserve">山</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">bīngmǎyǒng</t>
+          <t xml:space="preserve">shān</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">đội quân đất nung</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p06</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/15/Red_Apple.jpg/500px-Red_Apple.jpg</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">苹果</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">píngguǒ</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">quả táo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p07</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/1/17/Tiger_in_Ranthambhore.jpg/500px-Tiger_in_Ranthambhore.jpg</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">老虎</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lǎohǔ</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">con hổ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p08</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/9/98/Horse-and-pony.jpg/500px-Horse-and-pony.jpg</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">马</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mǎ</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">con ngựa</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p09</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/Full_Moon_Luc_Viatour.jpg/500px-Full_Moon_Luc_Viatour.jpg</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">月亮</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yuèliang</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mặt trăng</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p10</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/4/41/Fire.JPG/500px-Fire.JPG</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">huǒ</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lửa</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Mount_Everest_as_seen_from_Drukair2_PLW_edit.jpg/500px-Mount_Everest_as_seen_from_Drukair2_PLW_edit.jpg</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">山</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shān</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
         <is>
           <t xml:space="preserve">núi</t>
         </is>
@@ -6204,12 +5851,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Answer</t>
+          <t xml:space="preserve">Word</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pinyin</t>
+          <t xml:space="preserve">Phonetic</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -6253,22 +5900,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/8/8a/Zh-Beijing.ogg</t>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-book.ogg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">北京</t>
+          <t xml:space="preserve">book</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Běijīng</t>
+          <t xml:space="preserve">/bʊk/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bắc Kinh — thủ đô</t>
+          <t xml:space="preserve">quyển sách</t>
         </is>
       </c>
     </row>
@@ -6280,22 +5927,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/73/Zh-Shanghai.ogg</t>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-bread.ogg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">上海</t>
+          <t xml:space="preserve">bread</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shànghǎi</t>
+          <t xml:space="preserve">/bred/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thượng Hải</t>
+          <t xml:space="preserve">bánh mì</t>
         </is>
       </c>
     </row>
@@ -6307,22 +5954,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/8/82/Zh-Guangzhou.ogg</t>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-tree.ogg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">广州</t>
+          <t xml:space="preserve">tree</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guǎngzhōu</t>
+          <t xml:space="preserve">/triː/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quảng Châu</t>
+          <t xml:space="preserve">cái cây</t>
         </is>
       </c>
     </row>
@@ -6334,22 +5981,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/3/36/Zh-Hangzhou.ogg</t>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-river.ogg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">杭州</t>
+          <t xml:space="preserve">river</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hángzhōu</t>
+          <t xml:space="preserve">/ˈrɪvə/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hàng Châu</t>
+          <t xml:space="preserve">con sông</t>
         </is>
       </c>
     </row>
@@ -6361,22 +6008,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/9/9b/Zh-Tianjin.ogg</t>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-city.ogg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">天津</t>
+          <t xml:space="preserve">city</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiānjīn</t>
+          <t xml:space="preserve">/ˈsɪti/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thiên Tân</t>
+          <t xml:space="preserve">thành phố</t>
         </is>
       </c>
     </row>
@@ -6388,22 +6035,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/5/57/Zh-Anhui.ogg</t>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-night.ogg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">安徽</t>
+          <t xml:space="preserve">night</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ānhuī</t>
+          <t xml:space="preserve">/naɪt/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tỉnh An Huy</t>
+          <t xml:space="preserve">ban đêm</t>
         </is>
       </c>
     </row>
@@ -6415,22 +6062,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/2/25/Zh-Taiwan.ogg</t>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-music.ogg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">台湾</t>
+          <t xml:space="preserve">music</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Táiwān</t>
+          <t xml:space="preserve">/ˈmjuːzɪk/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đài Loan</t>
+          <t xml:space="preserve">âm nhạc</t>
         </is>
       </c>
     </row>
@@ -6442,22 +6089,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/9/9e/Zh-Changan.ogg</t>
+          <t xml:space="preserve">https://commons.wikimedia.org/wiki/Special:FilePath/En-us-teacher.ogg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">长安</t>
+          <t xml:space="preserve">teacher</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cháng'ān</t>
+          <t xml:space="preserve">/ˈtiːtʃə/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trường An — kinh đô thời Đường</t>
+          <t xml:space="preserve">giáo viên</t>
         </is>
       </c>
     </row>

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -22,6 +22,9 @@
     <sheet name="18 Grammar cloze (ngữ pháp)" sheetId="18" r:id="rId18"/>
     <sheet name="19 Dictation (nghe rồi gõ)" sheetId="19" r:id="rId19"/>
     <sheet name="20 Video lesson (bài video)" sheetId="20" r:id="rId20"/>
+    <sheet name="21 Formulas &amp; code (công thức)" sheetId="21" r:id="rId21"/>
+    <sheet name="22 Arabic (phải sang trái)" sheetId="22" r:id="rId22"/>
+    <sheet name="23 Vertical text (viết dọc)" sheetId="23" r:id="rId23"/>
   </sheets>
 </workbook>
 </file>
@@ -468,7 +471,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">side=back; size=90; type; tts=zh_CN</t>
+          <t xml:space="preserve">side=back; size=90; type; tts=zh_CN; font=sc; sort</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4773,6 +4776,656 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snippet</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; size=15; color=muted; label=Topic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; size=24; sort</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=26; math=block</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; code=python</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=15; color=muted; hint</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Geometry</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The area of a circle of radius r</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A = \pi r^2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The constant is the ratio of any circle's circumference to its diameter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Algebra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The quadratic formula</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x = \frac{-b \pm \sqrt{b^2 - 4ac}}{2a}</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The part under the root is the discriminant; its sign counts the roots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physics</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Einstein's mass–energy equivalence</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E = mc^2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c is the speed of light, so a very small mass is a very large energy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statistics</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The mean of n observations</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">\bar{x} = \frac{1}{n}\sum_{i=1}^{n} x_i</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sum them, divide by how many there were.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Python</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reverse a string</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">def backwards(text):
+    return text[::-1]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A slice with a step of -1 walks the string from the end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Python</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count how often each item appears</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from collections import Counter
+counts = Counter(words)
+print(counts.most_common(3))</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Counter is a dict that starts every key at zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SQL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows in one table with no match in another</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SELECT c.name
+FROM customers c
+LEFT JOIN orders o ON o.customer_id = c.id
+WHERE o.id IS NULL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A left join keeps every left row; the null is what says there was no match.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arabic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transliteration</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meaning</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rtl; size=44; font=serif; sort</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20; color=accent</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=14; color=muted; hint</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مرحبا</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marḥaban</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xin chào</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The everyday greeting, usable at any hour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">كتاب</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kitāb</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quyển sách</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same root as maktaba, a library or bookshop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ماء</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">māʼ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nước</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The last letter is a hamza, written on a seat here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بيت</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayt</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ngôi nhà</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Also a line of verse — a house of poetry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مدرسة</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madrasa</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trường học</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Literally a place of study.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شكرا</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shukran</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cảm ơn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answered with ʿafwan, you are welcome.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japanese</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reading</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vertical; font=jp; size=30; sort</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=18; color=accent</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">古池や蛙飛びこむ水の音</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ふるいけやかわずとびこむみずのおと</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ao xưa, ếch nhảy vào, tiếng nước khẽ vang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夏草や兵どもが夢の跡</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">なつくさやつわものどもがゆめのあと</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cỏ mùa hè — dấu vết giấc mộng của những người lính.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">秋深き隣は何をする人ぞ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">あきふかきとなりはなにをするひとぞ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thu đã sâu — người bên cạnh làm nghề gì nhỉ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">山は静かです</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">やまはしずかです</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Núi thì yên tĩnh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本を読みます</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ほんをよみます</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tôi đọc sách.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -25,6 +25,14 @@
     <sheet name="21 Formulas &amp; code (công thức)" sheetId="21" r:id="rId21"/>
     <sheet name="22 Arabic (phải sang trái)" sheetId="22" r:id="rId22"/>
     <sheet name="23 Vertical text (viết dọc)" sheetId="23" r:id="rId23"/>
+    <sheet name="24 Korean (tiếng Hàn)" sheetId="24" r:id="rId24"/>
+    <sheet name="25 Traditional (chữ phồn thể)" sheetId="25" r:id="rId25"/>
+    <sheet name="26 Shell commands (dòng lệnh)" sheetId="26" r:id="rId26"/>
+    <sheet name="27 Web dev (HTML &amp; JS)" sheetId="27" r:id="rId27"/>
+    <sheet name="28 Chemistry (hoá học)" sheetId="28" r:id="rId28"/>
+    <sheet name="29 Phrasal verbs (cụm động từ)" sheetId="29" r:id="rId29"/>
+    <sheet name="30 German (tiếng Đức)" sheetId="30" r:id="rId30"/>
+    <sheet name="31 Spanish (tiếng Tây Ban Nha)" sheetId="31" r:id="rId31"/>
   </sheets>
 </workbook>
 </file>
@@ -5426,6 +5434,1485 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Korean</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Romanisation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meaning</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font=kr; size=44; tts=ko_KR; sort</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20; color=accent</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=16; color=muted; italic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">학교</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hakgyo</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trường học</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저는 학교에 갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">친구</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chingu</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bạn bè</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">친구를 만났어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">음식</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eumsik</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">món ăn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한국 음식을 좋아해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">감사합니다</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gamsahamnida</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cảm ơn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도와주셔서 감사합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mul</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nước</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물 한 잔 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시간</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sigan</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thời gian</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시간이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">책</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chaek</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quyển sách</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이 책은 재미있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지하철</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jihacheol</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tàu điện ngầm</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지하철로 회사에 가요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traditional</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simplified</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pinyin</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font=tc; size=48; tts=zh_TW; sort</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=36; font=sc; color=muted; label=Simplified</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=22; color=accent</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">學習</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">学习</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xuéxí</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">học tập</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">電腦</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">电脑</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diànnǎo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">máy tính</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">圖書館</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">图书馆</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">túshūguǎn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thư viện</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">臺灣</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台湾</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Táiwān</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đài Loan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">醫生</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医生</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yīshēng</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bác sĩ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">餐廳</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">餐厅</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cāntīng</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nhà hàng</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">開車</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">开车</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kāichē</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lái xe</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">銀行</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">银行</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yínháng</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ngân hàng</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Group</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Task</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Command</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subdeck=1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; size=24; sort</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; code=bash</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=15; color=muted; hint</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Files</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">List every file, including the hidden ones</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ls -la</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The dot files are configuration; ls hides them by default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Files</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Find every .log file under this directory</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">find . -name '*.log'</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The quotes stop the shell expanding the pattern before find sees it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count the lines that contain a word</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grep -c 'error' app.log</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-c counts matching lines, not matches: two on one line is one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Show the last twenty lines and keep following the file</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tail -n 20 -f app.log</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-f holds the file open, which is how you watch a log live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Processes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">See what is listening on port 8000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lsof -i :8000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The command for the moment something says the address is in use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Undo the last commit but keep the changes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">git reset --soft HEAD~1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--soft keeps the work staged; --hard would throw it away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">See what changed in one file over time</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">git log -p -- src/app.py</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-p prints the patch of every commit that touched the path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Archives</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unpack a .tar.gz into a directory</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tar -xzf release.tar.gz -C build/</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x extracts, z is gzip, f names the file, -C says where to put it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Markup</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Script</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; size=22; sort</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; code=html</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; code=javascript</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=15; color=muted; hint</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">w01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How is a form field tied to its label?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;label for="email"&gt;Email&lt;/label&gt;
+&lt;input id="email" type="email"&gt;</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The for attribute matches the input's id, which is what makes the label clickable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">w02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What does defer do on a script tag?</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;script src="app.js" defer&gt;&lt;/script&gt;</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The file downloads in parallel and runs after the document is parsed, in order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">w03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How do you copy text to the clipboard?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">await navigator.clipboard.writeText('hello');</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only inside a user gesture, and only on https or localhost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">w04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How is a list built without innerHTML?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">const ul = document.createElement('ul');
+for (const item of items) {
+  const li = document.createElement('li');
+  li.textContent = item;
+  ul.append(li);
+}</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">textContent cannot execute anything; innerHTML with user text can.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">w05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How do you wait for an element to appear?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">new MutationObserver((_, obs) =&gt; {
+  const found = document.querySelector('.ready');
+  if (found) { obs.disconnect(); use(found); }
+}).observe(document.body, { childList: true, subtree: true });</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An observer costs nothing while nothing changes; a setInterval costs something forever.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answer</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equation</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subdeck=1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; size=22; sort</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=24; math=block</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=15; color=muted; hint</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reactions</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What does hydrogen burning in oxygen make?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nước.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2H_2 + O_2 \rightarrow 2H_2O</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balanced: the same atoms come out as went in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reactions</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What does an acid and a base make?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Muối và nước.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HCl + NaOH \rightarrow NaCl + H_2O</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neutralisation — the pH moves toward 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantities</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How many particles are in one mole?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khoảng 6,022 × 10²³ hạt.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N_A = 6.022 \times 10^{23}\ \mathrm{mol^{-1}}</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avogadro's number is a count, not a mass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantities</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How do you find the amount of a substance?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lấy khối lượng chia cho khối lượng mol.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n = \frac{m}{M}</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n in moles, m in grams, M in grams per mole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gases</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What is the ideal gas law?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Áp suất nhân thể tích bằng số mol nhân R nhân nhiệt độ.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pV = nRT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T is in kelvin, always — the law means nothing in celsius.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solutions</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How is molar concentration defined?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Số mol chất tan chia cho thể tích dung dịch.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c = \frac{n}{V}</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V is the volume of the solution, not of the solvent.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sentence</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meaning</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cloze; size=26; tts=en_US; sort</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=15; color=muted; hint</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I need to {{c1::look after}} my little brother tonight.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trông nom, chăm sóc</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Take care of. The particle cannot move: never look my brother after.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She {{c1::gave up}} smoking two years ago.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">từ bỏ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Give up + -ing, never give up to smoke.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We had to {{c1::put off}} the meeting until Friday.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hoãn lại</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postpone. This one does split: put the meeting off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He {{c1::ran into}} an old friend at the station.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tình cờ gặp</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Met by chance — nobody planned it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Please {{c1::fill in}} this form before you leave.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">điền vào</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">British fill in, American fill out, the same form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The car {{c1::broke down}} on the motorway.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hỏng, chết máy</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Of a machine. Of a person it means to weep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I will {{c1::look it up}} in the dictionary.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tra cứu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">With a pronoun the particle comes after it: never look up it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
@@ -5722,6 +7209,503 @@
       <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">Oxford 3000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Article</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Noun</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plural</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meaning</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; size=26; color=accent; label=Which article?</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=front; size=40; tts=de_DE; sort</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20; color=muted; label=Plural</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=20</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=16; italic; tts=de_DE; speed=0.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">der</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tisch</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">die Tische</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cái bàn</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Der Tisch steht am Fenster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">die</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tür</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">die Türen</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cái cửa</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bitte mach die Tür zu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">das</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fenster</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">die Fenster</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cửa sổ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das Fenster ist offen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">der</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Schlüssel</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">die Schlüssel</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chìa khoá</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich habe meinen Schlüssel vergessen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">die</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zeitung</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">die Zeitungen</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tờ báo</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er liest jeden Morgen die Zeitung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">das</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mädchen</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">die Mädchen</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cô bé</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jedes Wort auf -chen ist das.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">der</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bahnhof</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">die Bahnhöfe</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nhà ga</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wir treffen uns am Bahnhof.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">English</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spanish</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#config</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">size=28; sort</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=32; type=nc; tts=es_ES</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=15; color=muted</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the tree</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el árbol</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type=nc ignores the accent, so “el arbol” is accepted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the city</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la ciudad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the heart</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el corazón</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quickly</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rápidamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the mountain</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la montaña</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ñ is a letter of its own, not an accent — it has to be typed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the bird</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el pájaro</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tomorrow</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mañana</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Also means morning: mañana por la mañana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the river</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el río</t>
         </is>
       </c>
     </row>

--- a/examples/sheets2anki-examples.xlsx
+++ b/examples/sheets2anki-examples.xlsx
@@ -2549,15 +2549,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japanese</t>
+          <t xml:space="preserve">Word</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Phonetic</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Example</t>
         </is>
@@ -2571,17 +2576,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">size=40; furigana; tts=ja_JP</t>
+          <t xml:space="preserve">size=44; bold; tts=en_US; sort</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t xml:space="preserve">side=back; size=20; color=accent</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t xml:space="preserve">side=back; size=22</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">side=back; size=16; color=muted; italic; furigana</t>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">side=back; size=16; color=muted; italic; tts=en_US; speed=0.85</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2603,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">N5</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2608,22 +2618,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n5</t>
+          <t xml:space="preserve">cefr, b1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">食[た]べる</t>
+          <t xml:space="preserve">to afford</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ăn</t>
+          <t xml:space="preserve">/əˈfɔːd/</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">朝[あさ]ごはんを 食[た]べます。</t>
+          <t xml:space="preserve">đủ tiền để mua</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We cannot afford a bigger flat this year.</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2650,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N5</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2650,22 +2665,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n5</t>
+          <t xml:space="preserve">cefr, b1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">飲[の]む</t>
+          <t xml:space="preserve">to complain</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uống</t>
+          <t xml:space="preserve">/kəmˈpleɪn/</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">毎朝[まいあさ] コーヒーを 飲[の]みます。</t>
+          <t xml:space="preserve">phàn nàn</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She complained about the noise upstairs.</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2697,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">N5</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2692,22 +2712,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n5</t>
+          <t xml:space="preserve">cefr, b1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">行[い]く</t>
+          <t xml:space="preserve">to improve</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">đi</t>
+          <t xml:space="preserve">/ɪmˈpruːv/</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">来週[らいしゅう] 京都[きょうと]へ 行[い]きます。</t>
+          <t xml:space="preserve">cải thiện</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">His English improved after a year in Leeds.</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2744,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">N5</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2734,22 +2759,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n5</t>
+          <t xml:space="preserve">cefr, b1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">話[はな]す</t>
+          <t xml:space="preserve">to suggest</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">nói chuyện</t>
+          <t xml:space="preserve">/səˈdʒest/</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">日本語[にほんご]で 話[はな]しましょう。</t>
+          <t xml:space="preserve">gợi ý, đề nghị</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I suggest leaving before the traffic starts.</t>
         </is>
       </c>
     </row>
@@ -2761,12 +2791,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">N5</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2776,22 +2806,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n5</t>
+          <t xml:space="preserve">cefr, b1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">学校[がっこう]</t>
+          <t xml:space="preserve">advice</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">trường học</t>
+          <t xml:space="preserve">/ədˈvaɪs/</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">学校[がっこう]は 駅[えき]の 近[ちか]くです。</t>
+          <t xml:space="preserve">lời khuyên</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She gave me some good advice.</t>
         </is>
       </c>
     </row>
@@ -2803,12 +2838,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">N5</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2818,22 +2853,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n5</t>
+          <t xml:space="preserve">cefr, b1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">友[とも]だち</t>
+          <t xml:space="preserve">journey</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bạn bè</t>
+          <t xml:space="preserve">/ˈdʒɜːni/</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">友[とも]だちと 映画[えいが]を 見[み]ました。</t>
+          <t xml:space="preserve">chuyến đi</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The journey takes about four hours.</t>
         </is>
       </c>
     </row>
@@ -2845,12 +2885,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">N5</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2860,22 +2900,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n5</t>
+          <t xml:space="preserve">cefr, b1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">電車[でんしゃ]</t>
+          <t xml:space="preserve">neighbour</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">tàu điện</t>
+          <t xml:space="preserve">/ˈneɪbə/</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">電車[でんしゃ]で 会社[かいしゃ]へ 行[い]きます。</t>
+          <t xml:space="preserve">hàng xóm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Our neighbour looks after the cat.</t>
         </is>
       </c>
     </row>
@@ -2887,37 +2932,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">N5</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nouns</t>
+          <t xml:space="preserve">Adjectives</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n5</t>
+          <t xml:space="preserve">cefr, b1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">時間[じかん]</t>
+          <t xml:space="preserve">crowded</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">thời gian</t>
+          <t xml:space="preserve">/ˈkraʊdɪd/</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">今日[きょう]は 時間[じかん]が ありません。</t>
+          <t xml:space="preserve">đông đúc</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The market is crowded on Sunday mornings.</t>
         </is>
       </c>
     </row>
@@ -2929,12 +2979,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">N5</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2944,22 +2994,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n5</t>
+          <t xml:space="preserve">cefr, b1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">新[あたら]しい</t>
+          <t xml:space="preserve">reliable</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mới</t>
+          <t xml:space="preserve">/rɪˈlaɪəbl/</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">新[あたら]しい 本[ほん]を 買[か]いました。</t>
+          <t xml:space="preserve">đáng tin cậy</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He is the most reliable person on the team.</t>
         </is>
       </c>
     </row>
@@ -2971,37 +3026,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">N5</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjectives</t>
+          <t xml:space="preserve">Verbs</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n5</t>
+          <t xml:space="preserve">cefr, b2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">高[たか]い</t>
+          <t xml:space="preserve">to acknowledge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">cao; đắt</t>
+          <t xml:space="preserve">/əkˈnɒlɪdʒ/</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">この 店[みせ]は 少[すこ]し 高[たか]いです。</t>
+          <t xml:space="preserve">thừa nhận</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">She acknowledged that the plan had failed.</t>
         </is>
       </c>
     </row>
@@ -3013,37 +3073,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">N5</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjectives</t>
+          <t xml:space="preserve">Verbs</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n5</t>
+          <t xml:space="preserve">cefr, b2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">静[しず]か</t>
+          <t xml:space="preserve">to postpone</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">yên tĩnh</t>
+          <t xml:space="preserve">/pəˈspəʊn/</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">この 部屋[へや]は とても 静[しず]かです。</t>
+          <t xml:space="preserve">hoãn lại</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">They postponed the concert until March.</t>
         </is>
       </c>
     </row>
@@ -3055,37 +3120,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">N4</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verbs</t>
+          <t xml:space="preserve">Nouns</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n4</t>
+          <t xml:space="preserve">cefr, b2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">調[しら]べる</t>
+          <t xml:space="preserve">assumption</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">tra cứu; tìm hiểu</t>
+          <t xml:space="preserve">/əˈsʌmpʃn/</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">辞書[じしょ]で 言葉[ことば]を 調[しら]べます。</t>
+          <t xml:space="preserve">giả định</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The whole plan rests on one assumption.</t>
         </is>
       </c>
     </row>
@@ -3097,37 +3167,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">N4</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verbs</t>
+          <t xml:space="preserve">Nouns</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n4</t>
+          <t xml:space="preserve">cefr, b2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">続[つづ]ける</t>
+          <t xml:space="preserve">consequence</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">tiếp tục</t>
+          <t xml:space="preserve">/ˈkɒnsɪkwəns/</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">毎日[まいにち] 練習[れんしゅう]を 続[つづ]けます。</t>
+          <t xml:space="preserve">hậu quả</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nobody thought about the consequences.</t>
         </is>
       </c>
     </row>
@@ -3139,37 +3214,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">N4</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nouns</t>
+          <t xml:space="preserve">Adjectives</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n4</t>
+          <t xml:space="preserve">cefr, b2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">季節[きせつ]</t>
+          <t xml:space="preserve">thorough</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">mùa</t>
+          <t xml:space="preserve">/ˈθʌrə/</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">日本[にほん]には 四[よっ]つの 季節[きせつ]が あります。</t>
+          <t xml:space="preserve">kỹ lưỡng</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The report was thorough and easy to read.</t>
         </is>
       </c>
     </row>
@@ -3181,37 +3261,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLPT</t>
+          <t xml:space="preserve">English</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">N4</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nouns</t>
+          <t xml:space="preserve">Adjectives</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">jlpt, n4</t>
+          <t xml:space="preserve">cefr, b2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">桜[さくら]</t>
+          <t xml:space="preserve">reluctant</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">hoa anh đào</t>
+          <t xml:space="preserve">/rɪˈlʌktənt/</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">春[はる]に 桜[さくら]が 咲[さ]きます。</t>
+          <t xml:space="preserve">miễn cưỡng</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">He was reluctant to answer the question.</t>
         </is>
       </c>
     </row>
